--- a/03_Prompting/outputs/GPT/RESULT_clap_gpt-4o_fewshot.xlsx
+++ b/03_Prompting/outputs/GPT/RESULT_clap_gpt-4o_fewshot.xlsx
@@ -493,7 +493,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -6528,7 +6528,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -8024,7 +8024,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -8721,7 +8721,7 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -9061,7 +9061,7 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -9197,7 +9197,7 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -9469,7 +9469,7 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -10115,7 +10115,7 @@
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -10149,7 +10149,7 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -10353,7 +10353,7 @@
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -10506,7 +10506,7 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -11118,7 +11118,7 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -11628,7 +11628,7 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -11645,7 +11645,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -11713,7 +11713,7 @@
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -11815,7 +11815,7 @@
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -11951,7 +11951,7 @@
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -13396,7 +13396,7 @@
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -14484,7 +14484,7 @@
       </c>
       <c r="C827" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -14671,7 +14671,7 @@
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -15181,7 +15181,7 @@
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -15555,7 +15555,7 @@
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -15640,7 +15640,7 @@
       </c>
       <c r="C895" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -15742,7 +15742,7 @@
       </c>
       <c r="C901" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="C925" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -16490,7 +16490,7 @@
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="C957" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -17408,7 +17408,7 @@
       </c>
       <c r="C999" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -17425,7 +17425,7 @@
       </c>
       <c r="C1000" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -17459,7 +17459,7 @@
       </c>
       <c r="C1002" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -18020,7 +18020,7 @@
       </c>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -18139,7 +18139,7 @@
       </c>
       <c r="C1042" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -18173,7 +18173,7 @@
       </c>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -18326,7 +18326,7 @@
       </c>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -18377,7 +18377,7 @@
       </c>
       <c r="C1056" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -18411,7 +18411,7 @@
       </c>
       <c r="C1058" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -18581,7 +18581,7 @@
       </c>
       <c r="C1068" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -18887,7 +18887,7 @@
       </c>
       <c r="C1086" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -19567,7 +19567,7 @@
       </c>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -19822,7 +19822,7 @@
       </c>
       <c r="C1141" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -19924,7 +19924,7 @@
       </c>
       <c r="C1147" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -20230,7 +20230,7 @@
       </c>
       <c r="C1165" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -21148,7 +21148,7 @@
       </c>
       <c r="C1219" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -21250,7 +21250,7 @@
       </c>
       <c r="C1225" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -21624,7 +21624,7 @@
       </c>
       <c r="C1247" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -21879,7 +21879,7 @@
       </c>
       <c r="C1262" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -22202,7 +22202,7 @@
       </c>
       <c r="C1281" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -22729,7 +22729,7 @@
       </c>
       <c r="C1312" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -22831,7 +22831,7 @@
       </c>
       <c r="C1318" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -22865,7 +22865,7 @@
       </c>
       <c r="C1320" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -23443,7 +23443,7 @@
       </c>
       <c r="C1354" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -23460,7 +23460,7 @@
       </c>
       <c r="C1355" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -24582,7 +24582,7 @@
       </c>
       <c r="C1421" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -24701,7 +24701,7 @@
       </c>
       <c r="C1428" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -26146,7 +26146,7 @@
       </c>
       <c r="C1513" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -26435,7 +26435,7 @@
       </c>
       <c r="C1530" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -26452,7 +26452,7 @@
       </c>
       <c r="C1531" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -26503,7 +26503,7 @@
       </c>
       <c r="C1534" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -26945,7 +26945,7 @@
       </c>
       <c r="C1560" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -27030,7 +27030,7 @@
       </c>
       <c r="C1565" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -27047,7 +27047,7 @@
       </c>
       <c r="C1566" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -27064,7 +27064,7 @@
       </c>
       <c r="C1567" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -27217,7 +27217,7 @@
       </c>
       <c r="C1576" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -27455,7 +27455,7 @@
       </c>
       <c r="C1590" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -27880,7 +27880,7 @@
       </c>
       <c r="C1615" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -28016,7 +28016,7 @@
       </c>
       <c r="C1623" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -28220,7 +28220,7 @@
       </c>
       <c r="C1635" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -28271,7 +28271,7 @@
       </c>
       <c r="C1638" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -28288,7 +28288,7 @@
       </c>
       <c r="C1639" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -28305,7 +28305,7 @@
       </c>
       <c r="C1640" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -28373,7 +28373,7 @@
       </c>
       <c r="C1644" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -28526,7 +28526,7 @@
       </c>
       <c r="C1653" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -28577,7 +28577,7 @@
       </c>
       <c r="C1656" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -28645,7 +28645,7 @@
       </c>
       <c r="C1660" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -28781,7 +28781,7 @@
       </c>
       <c r="C1668" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -28866,7 +28866,7 @@
       </c>
       <c r="C1673" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -29155,7 +29155,7 @@
       </c>
       <c r="C1690" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -29172,7 +29172,7 @@
       </c>
       <c r="C1691" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -29478,7 +29478,7 @@
       </c>
       <c r="C1709" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -29495,7 +29495,7 @@
       </c>
       <c r="C1710" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -29546,7 +29546,7 @@
       </c>
       <c r="C1713" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -29597,7 +29597,7 @@
       </c>
       <c r="C1716" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -29767,7 +29767,7 @@
       </c>
       <c r="C1726" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -29835,7 +29835,7 @@
       </c>
       <c r="C1730" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -30107,7 +30107,7 @@
       </c>
       <c r="C1746" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -30175,7 +30175,7 @@
       </c>
       <c r="C1750" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -30311,7 +30311,7 @@
       </c>
       <c r="C1758" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -30362,7 +30362,7 @@
       </c>
       <c r="C1761" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -30685,7 +30685,7 @@
       </c>
       <c r="C1780" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -30872,7 +30872,7 @@
       </c>
       <c r="C1791" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -30940,7 +30940,7 @@
       </c>
       <c r="C1795" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -31450,7 +31450,7 @@
       </c>
       <c r="C1825" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -31467,7 +31467,7 @@
       </c>
       <c r="C1826" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -31637,7 +31637,7 @@
       </c>
       <c r="C1836" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -31705,7 +31705,7 @@
       </c>
       <c r="C1840" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -31722,7 +31722,7 @@
       </c>
       <c r="C1841" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -31756,7 +31756,7 @@
       </c>
       <c r="C1843" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -32249,7 +32249,7 @@
       </c>
       <c r="C1872" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -32266,7 +32266,7 @@
       </c>
       <c r="C1873" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -32385,7 +32385,7 @@
       </c>
       <c r="C1880" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -32453,7 +32453,7 @@
       </c>
       <c r="C1884" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -32572,7 +32572,7 @@
       </c>
       <c r="C1891" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -32623,7 +32623,7 @@
       </c>
       <c r="C1894" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -32793,7 +32793,7 @@
       </c>
       <c r="C1904" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -32997,7 +32997,7 @@
       </c>
       <c r="C1916" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -33048,7 +33048,7 @@
       </c>
       <c r="C1919" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -33252,7 +33252,7 @@
       </c>
       <c r="C1931" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -33541,7 +33541,7 @@
       </c>
       <c r="C1948" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -33558,7 +33558,7 @@
       </c>
       <c r="C1949" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -33728,7 +33728,7 @@
       </c>
       <c r="C1959" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -33966,7 +33966,7 @@
       </c>
       <c r="C1973" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -34068,7 +34068,7 @@
       </c>
       <c r="C1979" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -34629,7 +34629,7 @@
       </c>
       <c r="C2012" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -35207,7 +35207,7 @@
       </c>
       <c r="C2046" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -35462,7 +35462,7 @@
       </c>
       <c r="C2061" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -35513,7 +35513,7 @@
       </c>
       <c r="C2064" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -35938,7 +35938,7 @@
       </c>
       <c r="C2089" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36108,7 +36108,7 @@
       </c>
       <c r="C2099" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36414,7 +36414,7 @@
       </c>
       <c r="C2117" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37179,7 +37179,7 @@
       </c>
       <c r="C2162" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37638,7 +37638,7 @@
       </c>
       <c r="C2189" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37689,7 +37689,7 @@
       </c>
       <c r="C2192" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37774,7 +37774,7 @@
       </c>
       <c r="C2197" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37927,7 +37927,7 @@
       </c>
       <c r="C2206" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -38080,7 +38080,7 @@
       </c>
       <c r="C2215" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -38114,7 +38114,7 @@
       </c>
       <c r="C2217" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -38131,7 +38131,7 @@
       </c>
       <c r="C2218" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -38148,7 +38148,7 @@
       </c>
       <c r="C2219" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -38233,7 +38233,7 @@
       </c>
       <c r="C2224" t="inlineStr">
         <is>
-          <t>SECURITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -38369,7 +38369,7 @@
       </c>
       <c r="C2232" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -38386,7 +38386,7 @@
       </c>
       <c r="C2233" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -38420,7 +38420,7 @@
       </c>
       <c r="C2235" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -38454,7 +38454,7 @@
       </c>
       <c r="C2237" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -39219,7 +39219,7 @@
       </c>
       <c r="C2282" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -39440,7 +39440,7 @@
       </c>
       <c r="C2295" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -39525,7 +39525,7 @@
       </c>
       <c r="C2300" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -39593,7 +39593,7 @@
       </c>
       <c r="C2304" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -39712,7 +39712,7 @@
       </c>
       <c r="C2311" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -40392,7 +40392,7 @@
       </c>
       <c r="C2351" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40528,7 +40528,7 @@
       </c>
       <c r="C2359" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40579,7 +40579,7 @@
       </c>
       <c r="C2362" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40715,7 +40715,7 @@
       </c>
       <c r="C2370" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -41072,7 +41072,7 @@
       </c>
       <c r="C2391" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41344,7 +41344,7 @@
       </c>
       <c r="C2407" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -41395,7 +41395,7 @@
       </c>
       <c r="C2410" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41565,7 +41565,7 @@
       </c>
       <c r="C2420" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41650,7 +41650,7 @@
       </c>
       <c r="C2425" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41956,7 +41956,7 @@
       </c>
       <c r="C2443" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -41990,7 +41990,7 @@
       </c>
       <c r="C2445" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -42211,7 +42211,7 @@
       </c>
       <c r="C2458" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -42381,7 +42381,7 @@
       </c>
       <c r="C2468" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -42568,7 +42568,7 @@
       </c>
       <c r="C2479" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -43044,7 +43044,7 @@
       </c>
       <c r="C2507" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -43078,7 +43078,7 @@
       </c>
       <c r="C2509" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -43095,7 +43095,7 @@
       </c>
       <c r="C2510" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -43129,7 +43129,7 @@
       </c>
       <c r="C2512" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -43214,7 +43214,7 @@
       </c>
       <c r="C2517" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -43248,7 +43248,7 @@
       </c>
       <c r="C2519" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -43452,7 +43452,7 @@
       </c>
       <c r="C2531" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -43469,7 +43469,7 @@
       </c>
       <c r="C2532" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -43571,7 +43571,7 @@
       </c>
       <c r="C2538" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -43690,7 +43690,7 @@
       </c>
       <c r="C2545" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -43758,7 +43758,7 @@
       </c>
       <c r="C2549" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -43843,7 +43843,7 @@
       </c>
       <c r="C2554" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -43894,7 +43894,7 @@
       </c>
       <c r="C2557" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -44030,7 +44030,7 @@
       </c>
       <c r="C2565" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -44047,7 +44047,7 @@
       </c>
       <c r="C2566" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -44115,7 +44115,7 @@
       </c>
       <c r="C2570" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -44149,7 +44149,7 @@
       </c>
       <c r="C2572" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -44251,7 +44251,7 @@
       </c>
       <c r="C2578" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -44438,7 +44438,7 @@
       </c>
       <c r="C2589" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -44506,7 +44506,7 @@
       </c>
       <c r="C2593" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -44574,7 +44574,7 @@
       </c>
       <c r="C2597" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -44642,7 +44642,7 @@
       </c>
       <c r="C2601" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -44846,7 +44846,7 @@
       </c>
       <c r="C2613" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -44965,7 +44965,7 @@
       </c>
       <c r="C2620" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -45050,7 +45050,7 @@
       </c>
       <c r="C2625" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -45169,7 +45169,7 @@
       </c>
       <c r="C2632" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -45424,7 +45424,7 @@
       </c>
       <c r="C2647" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -45679,7 +45679,7 @@
       </c>
       <c r="C2662" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -45696,7 +45696,7 @@
       </c>
       <c r="C2663" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -46002,7 +46002,7 @@
       </c>
       <c r="C2681" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -46036,7 +46036,7 @@
       </c>
       <c r="C2683" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -46121,7 +46121,7 @@
       </c>
       <c r="C2688" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -46342,7 +46342,7 @@
       </c>
       <c r="C2701" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -46444,7 +46444,7 @@
       </c>
       <c r="C2707" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -46580,7 +46580,7 @@
       </c>
       <c r="C2715" t="inlineStr">
         <is>
-          <t>SECURITY</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -46767,7 +46767,7 @@
       </c>
       <c r="C2726" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -47022,7 +47022,7 @@
       </c>
       <c r="C2741" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -47362,7 +47362,7 @@
       </c>
       <c r="C2761" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -47379,7 +47379,7 @@
       </c>
       <c r="C2762" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -47515,7 +47515,7 @@
       </c>
       <c r="C2770" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -47532,7 +47532,7 @@
       </c>
       <c r="C2771" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -47583,7 +47583,7 @@
       </c>
       <c r="C2774" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -47617,7 +47617,7 @@
       </c>
       <c r="C2776" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -47685,7 +47685,7 @@
       </c>
       <c r="C2780" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -47702,7 +47702,7 @@
       </c>
       <c r="C2781" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -47838,7 +47838,7 @@
       </c>
       <c r="C2789" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -47923,7 +47923,7 @@
       </c>
       <c r="C2794" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -47940,7 +47940,7 @@
       </c>
       <c r="C2795" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -48059,7 +48059,7 @@
       </c>
       <c r="C2802" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -48076,7 +48076,7 @@
       </c>
       <c r="C2803" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -48110,7 +48110,7 @@
       </c>
       <c r="C2805" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -48178,7 +48178,7 @@
       </c>
       <c r="C2809" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -48195,7 +48195,7 @@
       </c>
       <c r="C2810" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -48348,7 +48348,7 @@
       </c>
       <c r="C2819" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -48382,7 +48382,7 @@
       </c>
       <c r="C2821" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -48518,7 +48518,7 @@
       </c>
       <c r="C2829" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -48722,7 +48722,7 @@
       </c>
       <c r="C2841" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -48739,7 +48739,7 @@
       </c>
       <c r="C2842" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -48756,7 +48756,7 @@
       </c>
       <c r="C2843" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -48807,7 +48807,7 @@
       </c>
       <c r="C2846" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -48977,7 +48977,7 @@
       </c>
       <c r="C2856" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -49028,7 +49028,7 @@
       </c>
       <c r="C2859" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -49368,7 +49368,7 @@
       </c>
       <c r="C2879" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -50116,7 +50116,7 @@
       </c>
       <c r="C2923" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -50252,7 +50252,7 @@
       </c>
       <c r="C2931" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -50711,7 +50711,7 @@
       </c>
       <c r="C2958" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -50966,7 +50966,7 @@
       </c>
       <c r="C2973" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -51034,7 +51034,7 @@
       </c>
       <c r="C2977" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>SECURITY</t>
         </is>
       </c>
     </row>
@@ -51170,7 +51170,7 @@
       </c>
       <c r="C2985" t="inlineStr">
         <is>
-          <t>SECURITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -51289,7 +51289,7 @@
       </c>
       <c r="C2992" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>SECURITY</t>
         </is>
       </c>
     </row>
@@ -51479,7 +51479,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8556666666666667</v>
+        <v>0.856</v>
       </c>
     </row>
     <row r="3">
@@ -51489,7 +51489,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7542163256308015</v>
+        <v>0.7491064830188809</v>
       </c>
     </row>
     <row r="4">
@@ -51499,7 +51499,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8597001173949448</v>
+        <v>0.8610771645860096</v>
       </c>
     </row>
     <row r="5">
@@ -51509,7 +51509,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7414138684707618</v>
+        <v>0.7410910232402763</v>
       </c>
     </row>
     <row r="6">
@@ -51519,7 +51519,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7776477198688657</v>
+        <v>0.7724947416292824</v>
       </c>
     </row>
     <row r="7">
@@ -51529,7 +51529,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>718.3303982439998</v>
+        <v>1616.641422658999</v>
       </c>
     </row>
     <row r="8">
@@ -51539,7 +51539,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2394434660813332</v>
+        <v>0.5388804742196662</v>
       </c>
     </row>
   </sheetData>
